--- a/output/2026-09-05_20_Slovenia_Pomurska_Depolverazione_Trattamento_aria.xlsx
+++ b/output/2026-09-05_20_Slovenia_Pomurska_Depolverazione_Trattamento_aria.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -632,7 +632,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -657,8 +657,6 @@
           <t>Depolverazione / Trattamento aria</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Esistenza confermata da più fonti indipendenti (letakonosa.si, kimbino.si, odpiralnicasi.com). Indirizzo civico esatto e contatti non reperiti con certezza nelle fonti pubbliche consultate - lasciati vuoti.</t>
@@ -666,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
